--- a/data/gravel/Specialized Crux 2025.xlsx
+++ b/data/gravel/Specialized Crux 2025.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10608"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10713"/>
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/walker/Documents/Github/Bike Geometry Project/data/gravel/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{39CCDB82-A87D-6348-B4AC-970CF9A57E91}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D1A605F4-F3EA-7D45-A57D-784DEA74C21E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="500" windowWidth="28800" windowHeight="17500" xr2:uid="{AE0F04AA-80E5-8247-9791-D6B95FAD9AB5}"/>
+    <workbookView xWindow="0" yWindow="2100" windowWidth="25020" windowHeight="11320" xr2:uid="{AE0F04AA-80E5-8247-9791-D6B95FAD9AB5}"/>
   </bookViews>
   <sheets>
     <sheet name="Specialized Crux 2025" sheetId="1" r:id="rId1"/>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="72" uniqueCount="71">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="113" uniqueCount="108">
   <si>
     <t>brand</t>
   </si>
@@ -62,9 +62,6 @@
     <t>frame weight</t>
   </si>
   <si>
-    <t>UDH</t>
-  </si>
-  <si>
     <t>yes</t>
   </si>
   <si>
@@ -206,49 +203,163 @@
     <t>Specialized</t>
   </si>
   <si>
+    <t>https://www.specialized.com/us/en/s-works-crux-sram-red-xplr/p/4223480?color=5381911-4223480</t>
+  </si>
+  <si>
+    <t>front_center</t>
+  </si>
+  <si>
+    <t>saddle_width</t>
+  </si>
+  <si>
+    <t>seatpost_length</t>
+  </si>
+  <si>
+    <t>bb_height</t>
+  </si>
+  <si>
+    <t>Height (Cm)</t>
+  </si>
+  <si>
+    <t>Size </t>
+  </si>
+  <si>
+    <t>155-158</t>
+  </si>
+  <si>
+    <t>163-168</t>
+  </si>
+  <si>
+    <t>168-175</t>
+  </si>
+  <si>
+    <t>175-183</t>
+  </si>
+  <si>
+    <t>183-191</t>
+  </si>
+  <si>
+    <t>191-198</t>
+  </si>
+  <si>
+    <t>udh</t>
+  </si>
+  <si>
+    <t>dropout</t>
+  </si>
+  <si>
+    <t>650B tire max</t>
+  </si>
+  <si>
+    <t>suspension corrected</t>
+  </si>
+  <si>
+    <t>rear axle</t>
+  </si>
+  <si>
+    <t>front axle</t>
+  </si>
+  <si>
+    <t>q-factor</t>
+  </si>
+  <si>
+    <t>seatpost diameter</t>
+  </si>
+  <si>
+    <t>routing shifter</t>
+  </si>
+  <si>
+    <t>routing dropper</t>
+  </si>
+  <si>
+    <t>routing dynamo</t>
+  </si>
+  <si>
+    <t>front derailleur</t>
+  </si>
+  <si>
+    <t>chainring 1</t>
+  </si>
+  <si>
+    <t>chainring 2</t>
+  </si>
+  <si>
+    <t>bottom bracket</t>
+  </si>
+  <si>
+    <t>mounts inner</t>
+  </si>
+  <si>
+    <t>mounts under</t>
+  </si>
+  <si>
+    <t>mounts top</t>
+  </si>
+  <si>
+    <t>mounts fork</t>
+  </si>
+  <si>
+    <t>mounts fender rear</t>
+  </si>
+  <si>
+    <t>mounts fender front</t>
+  </si>
+  <si>
+    <t>mounts rack</t>
+  </si>
+  <si>
+    <t>rotor max front</t>
+  </si>
+  <si>
+    <t>rotor max rear</t>
+  </si>
+  <si>
+    <t>frameset</t>
+  </si>
+  <si>
+    <t>base build</t>
+  </si>
+  <si>
+    <t>currency</t>
+  </si>
+  <si>
+    <t>Notes</t>
+  </si>
+  <si>
+    <t>1. An adapter plate for a front derailleur can be purchased</t>
+  </si>
+  <si>
+    <t>adapter</t>
+  </si>
+  <si>
+    <t>us</t>
+  </si>
+  <si>
     <t>Crux</t>
   </si>
   <si>
-    <t>https://www.specialized.com/us/en/s-works-crux-sram-red-xplr/p/4223480?color=5381911-4223480</t>
-  </si>
-  <si>
-    <t>front_center</t>
-  </si>
-  <si>
-    <t>saddle_width</t>
-  </si>
-  <si>
-    <t>seatpost_length</t>
-  </si>
-  <si>
-    <t>bb_height</t>
-  </si>
-  <si>
-    <t>Height (Cm)</t>
-  </si>
-  <si>
-    <t>Size </t>
-  </si>
-  <si>
-    <t>155-158</t>
-  </si>
-  <si>
-    <t>163-168</t>
-  </si>
-  <si>
-    <t>168-175</t>
-  </si>
-  <si>
-    <t>175-183</t>
-  </si>
-  <si>
-    <t>183-191</t>
-  </si>
-  <si>
-    <t>191-198</t>
-  </si>
-  <si>
-    <t>a10:h36</t>
+    <t>fork suspension</t>
+  </si>
+  <si>
+    <t>stem suspension</t>
+  </si>
+  <si>
+    <t>rear suspension</t>
+  </si>
+  <si>
+    <t>no</t>
+  </si>
+  <si>
+    <t>internal storage</t>
+  </si>
+  <si>
+    <t>a10:h37</t>
+  </si>
+  <si>
+    <t>700c width max</t>
+  </si>
+  <si>
+    <t>ISO ASTM</t>
   </si>
 </sst>
 </file>
@@ -258,7 +369,7 @@
   <numFmts count="1">
     <numFmt numFmtId="164" formatCode="0.0"/>
   </numFmts>
-  <fonts count="19" x14ac:knownFonts="1">
+  <fonts count="20" x14ac:knownFonts="1">
     <font>
       <sz val="12"/>
       <color theme="1"/>
@@ -370,6 +481,12 @@
       <color rgb="FF252525"/>
       <name val="Futura Medium"/>
     </font>
+    <font>
+      <sz val="14"/>
+      <color theme="1"/>
+      <name val="Futura"/>
+      <family val="2"/>
+    </font>
   </fonts>
   <fills count="2">
     <fill>
@@ -391,7 +508,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="23">
+  <cellXfs count="25">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="15" fontId="1" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
@@ -415,6 +532,10 @@
     <xf numFmtId="0" fontId="16" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="17" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="18" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="0" borderId="0" xfId="0" applyFont="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -534,13 +655,13 @@
     <xdr:from>
       <xdr:col>1</xdr:col>
       <xdr:colOff>1562100</xdr:colOff>
-      <xdr:row>39</xdr:row>
+      <xdr:row>40</xdr:row>
       <xdr:rowOff>76200</xdr:rowOff>
     </xdr:from>
     <xdr:to>
-      <xdr:col>14</xdr:col>
-      <xdr:colOff>228600</xdr:colOff>
-      <xdr:row>64</xdr:row>
+      <xdr:col>13</xdr:col>
+      <xdr:colOff>330200</xdr:colOff>
+      <xdr:row>65</xdr:row>
       <xdr:rowOff>76200</xdr:rowOff>
     </xdr:to>
     <xdr:pic>
@@ -911,34 +1032,35 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{299AF885-3999-4E4F-8F92-5857EF0F7F08}">
-  <dimension ref="A1:S45"/>
+  <dimension ref="A1:AH68"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="20" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="29.33203125" style="1" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="31.83203125" style="1" customWidth="1"/>
-    <col min="3" max="8" width="11" style="1" bestFit="1" customWidth="1"/>
-    <col min="9" max="9" width="10.83203125" style="1"/>
+    <col min="3" max="5" width="11" style="1" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="13.5" style="1" customWidth="1"/>
+    <col min="7" max="9" width="13.33203125" style="1" customWidth="1"/>
     <col min="10" max="24" width="11" style="1" bestFit="1" customWidth="1"/>
     <col min="25" max="16384" width="10.83203125" style="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:34" x14ac:dyDescent="0.3">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>55</v>
-      </c>
-    </row>
-    <row r="2" spans="1:17" x14ac:dyDescent="0.3">
+        <v>54</v>
+      </c>
+    </row>
+    <row r="2" spans="1:34" x14ac:dyDescent="0.3">
       <c r="A2" s="1" t="s">
         <v>1</v>
       </c>
       <c r="B2" s="1" t="s">
-        <v>56</v>
-      </c>
-    </row>
-    <row r="3" spans="1:17" x14ac:dyDescent="0.3">
+        <v>99</v>
+      </c>
+    </row>
+    <row r="3" spans="1:34" x14ac:dyDescent="0.3">
       <c r="A3" s="1" t="s">
         <v>2</v>
       </c>
@@ -946,7 +1068,7 @@
         <v>2025</v>
       </c>
     </row>
-    <row r="4" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="4" spans="1:34" x14ac:dyDescent="0.3">
       <c r="A4" s="1" t="s">
         <v>3</v>
       </c>
@@ -954,49 +1076,191 @@
         <v>45855</v>
       </c>
     </row>
-    <row r="5" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="5" spans="1:34" x14ac:dyDescent="0.3">
       <c r="A5" s="1" t="s">
         <v>4</v>
       </c>
       <c r="B5" s="1" t="s">
-        <v>57</v>
-      </c>
-    </row>
-    <row r="6" spans="1:17" x14ac:dyDescent="0.3">
-      <c r="A6" s="1" t="s">
+        <v>55</v>
+      </c>
+    </row>
+    <row r="6" spans="1:34" customFormat="1" ht="55" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A6" s="23" t="s">
         <v>5</v>
       </c>
-      <c r="B6" s="1" t="s">
+      <c r="B6" s="23" t="s">
+        <v>68</v>
+      </c>
+      <c r="C6" s="23" t="s">
+        <v>69</v>
+      </c>
+      <c r="D6" s="23" t="s">
+        <v>106</v>
+      </c>
+      <c r="E6" s="23" t="s">
+        <v>70</v>
+      </c>
+      <c r="F6" s="23" t="s">
+        <v>71</v>
+      </c>
+      <c r="G6" s="23" t="s">
+        <v>100</v>
+      </c>
+      <c r="H6" s="23" t="s">
+        <v>101</v>
+      </c>
+      <c r="I6" s="23" t="s">
+        <v>102</v>
+      </c>
+      <c r="J6" s="23" t="s">
+        <v>72</v>
+      </c>
+      <c r="K6" s="23" t="s">
+        <v>73</v>
+      </c>
+      <c r="L6" s="23" t="s">
+        <v>74</v>
+      </c>
+      <c r="M6" s="23" t="s">
+        <v>75</v>
+      </c>
+      <c r="N6" s="23" t="s">
+        <v>76</v>
+      </c>
+      <c r="O6" s="23" t="s">
+        <v>77</v>
+      </c>
+      <c r="P6" s="23" t="s">
+        <v>78</v>
+      </c>
+      <c r="Q6" s="23" t="s">
+        <v>79</v>
+      </c>
+      <c r="R6" s="23" t="s">
+        <v>80</v>
+      </c>
+      <c r="S6" s="23" t="s">
+        <v>81</v>
+      </c>
+      <c r="T6" s="23" t="s">
+        <v>82</v>
+      </c>
+      <c r="U6" s="23" t="s">
+        <v>83</v>
+      </c>
+      <c r="V6" s="23" t="s">
+        <v>84</v>
+      </c>
+      <c r="W6" s="23" t="s">
+        <v>85</v>
+      </c>
+      <c r="X6" s="23" t="s">
+        <v>86</v>
+      </c>
+      <c r="Y6" s="23" t="s">
+        <v>87</v>
+      </c>
+      <c r="Z6" s="23" t="s">
+        <v>88</v>
+      </c>
+      <c r="AA6" s="23" t="s">
+        <v>89</v>
+      </c>
+      <c r="AB6" s="24" t="s">
+        <v>107</v>
+      </c>
+      <c r="AC6" s="23" t="s">
+        <v>90</v>
+      </c>
+      <c r="AD6" s="23" t="s">
+        <v>91</v>
+      </c>
+      <c r="AE6" s="23" t="s">
+        <v>92</v>
+      </c>
+      <c r="AF6" s="23" t="s">
+        <v>93</v>
+      </c>
+      <c r="AG6" s="23" t="s">
+        <v>94</v>
+      </c>
+      <c r="AH6" s="23" t="s">
+        <v>104</v>
+      </c>
+    </row>
+    <row r="7" spans="1:34" x14ac:dyDescent="0.3">
+      <c r="A7" s="1" t="s">
         <v>6</v>
       </c>
-    </row>
-    <row r="7" spans="1:17" x14ac:dyDescent="0.3">
-      <c r="A7" s="1" t="s">
-        <v>7</v>
-      </c>
-    </row>
-    <row r="8" spans="1:17" x14ac:dyDescent="0.3">
-      <c r="A8" s="1" t="s">
+      <c r="B7" s="1" t="s">
         <v>8</v>
       </c>
-      <c r="B8" s="1" t="s">
+      <c r="C7" s="1">
+        <v>0</v>
+      </c>
+      <c r="D7" s="1">
+        <v>47</v>
+      </c>
+      <c r="E7" s="1">
+        <v>2.1</v>
+      </c>
+      <c r="F7" s="1" t="s">
+        <v>103</v>
+      </c>
+      <c r="G7" s="1" t="s">
+        <v>103</v>
+      </c>
+      <c r="H7" s="1" t="s">
+        <v>103</v>
+      </c>
+      <c r="I7" s="1" t="s">
+        <v>103</v>
+      </c>
+      <c r="J7" s="1">
+        <v>142</v>
+      </c>
+      <c r="K7" s="1">
+        <v>100</v>
+      </c>
+      <c r="M7" s="1">
+        <v>31.6</v>
+      </c>
+      <c r="Q7" s="1" t="s">
+        <v>97</v>
+      </c>
+      <c r="U7" s="1">
+        <v>2</v>
+      </c>
+      <c r="V7" s="1">
+        <v>1</v>
+      </c>
+      <c r="AE7" s="1">
+        <v>2999</v>
+      </c>
+      <c r="AF7" s="1">
+        <v>3799</v>
+      </c>
+      <c r="AG7" s="1" t="s">
+        <v>98</v>
+      </c>
+      <c r="AH7" s="1" t="s">
+        <v>103</v>
+      </c>
+    </row>
+    <row r="9" spans="1:34" x14ac:dyDescent="0.3">
+      <c r="A9" s="1" t="s">
         <v>9</v>
       </c>
-    </row>
-    <row r="9" spans="1:17" x14ac:dyDescent="0.3">
-      <c r="A9" s="1" t="s">
+      <c r="B9" s="1" t="s">
+        <v>105</v>
+      </c>
+    </row>
+    <row r="10" spans="1:34" x14ac:dyDescent="0.3">
+      <c r="A10" s="1" t="s">
         <v>10</v>
       </c>
-      <c r="B9" s="1" t="s">
-        <v>70</v>
-      </c>
-    </row>
-    <row r="10" spans="1:17" x14ac:dyDescent="0.3">
-      <c r="A10" s="1" t="s">
-        <v>11</v>
-      </c>
       <c r="B10" s="1" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="C10" s="21">
         <v>49</v>
@@ -1025,12 +1289,12 @@
       <c r="P10" s="3"/>
       <c r="Q10" s="3"/>
     </row>
-    <row r="11" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="11" spans="1:34" x14ac:dyDescent="0.3">
       <c r="A11" s="1" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="B11" s="22" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="C11" s="22">
         <v>165</v>
@@ -1059,12 +1323,12 @@
       <c r="P11" s="3"/>
       <c r="Q11" s="3"/>
     </row>
-    <row r="12" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="12" spans="1:34" x14ac:dyDescent="0.3">
       <c r="A12" s="1" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="B12" s="22" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="C12" s="22">
         <v>380</v>
@@ -1093,12 +1357,12 @@
       <c r="P12" s="3"/>
       <c r="Q12" s="3"/>
     </row>
-    <row r="13" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="13" spans="1:34" x14ac:dyDescent="0.3">
       <c r="A13" s="1" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="B13" s="22" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="C13" s="22">
         <v>70</v>
@@ -1127,12 +1391,12 @@
       <c r="P13" s="3"/>
       <c r="Q13" s="3"/>
     </row>
-    <row r="14" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="14" spans="1:34" x14ac:dyDescent="0.3">
       <c r="A14" s="1" t="s">
-        <v>59</v>
+        <v>57</v>
       </c>
       <c r="B14" s="22" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="C14" s="22">
         <v>155</v>
@@ -1161,12 +1425,12 @@
       <c r="P14" s="3"/>
       <c r="Q14" s="3"/>
     </row>
-    <row r="15" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="15" spans="1:34" x14ac:dyDescent="0.3">
       <c r="A15" s="1" t="s">
-        <v>60</v>
+        <v>58</v>
       </c>
       <c r="B15" s="22" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="C15" s="22">
         <v>300</v>
@@ -1195,12 +1459,12 @@
       <c r="P15" s="3"/>
       <c r="Q15" s="3"/>
     </row>
-    <row r="16" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="16" spans="1:34" x14ac:dyDescent="0.3">
       <c r="A16" s="1" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="B16" s="22" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="C16" s="22">
         <v>530</v>
@@ -1231,10 +1495,10 @@
     </row>
     <row r="17" spans="1:19" x14ac:dyDescent="0.3">
       <c r="A17" s="1" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="B17" s="22" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="C17" s="22">
         <v>375</v>
@@ -1265,10 +1529,10 @@
     </row>
     <row r="18" spans="1:19" x14ac:dyDescent="0.3">
       <c r="A18" s="1" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="B18" s="22" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="C18" s="22">
         <v>100</v>
@@ -1301,10 +1565,10 @@
     </row>
     <row r="19" spans="1:19" x14ac:dyDescent="0.3">
       <c r="A19" s="1" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="B19" s="22" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="C19" s="22">
         <v>70.5</v>
@@ -1337,10 +1601,10 @@
     </row>
     <row r="20" spans="1:19" x14ac:dyDescent="0.3">
       <c r="A20" s="1" t="s">
-        <v>61</v>
+        <v>59</v>
       </c>
       <c r="B20" s="22" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="C20" s="22">
         <v>284</v>
@@ -1373,10 +1637,10 @@
     </row>
     <row r="21" spans="1:19" x14ac:dyDescent="0.3">
       <c r="A21" s="1" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="B21" s="22" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="C21" s="22">
         <v>74</v>
@@ -1409,10 +1673,10 @@
     </row>
     <row r="22" spans="1:19" x14ac:dyDescent="0.3">
       <c r="A22" s="1" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="B22" s="22" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="C22" s="22">
         <v>74</v>
@@ -1445,10 +1709,10 @@
     </row>
     <row r="23" spans="1:19" x14ac:dyDescent="0.3">
       <c r="A23" s="1" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="B23" s="22" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="C23" s="22">
         <v>401</v>
@@ -1470,10 +1734,10 @@
       </c>
       <c r="J23" s="13"/>
       <c r="K23" s="18" t="s">
-        <v>62</v>
+        <v>60</v>
       </c>
       <c r="L23" s="18" t="s">
-        <v>63</v>
+        <v>61</v>
       </c>
       <c r="M23" s="13"/>
       <c r="N23" s="13"/>
@@ -1485,10 +1749,10 @@
     </row>
     <row r="24" spans="1:19" x14ac:dyDescent="0.3">
       <c r="A24" s="1" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="B24" s="22" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="C24" s="22">
         <v>50</v>
@@ -1510,7 +1774,7 @@
       </c>
       <c r="J24" s="13"/>
       <c r="K24" s="19" t="s">
-        <v>64</v>
+        <v>62</v>
       </c>
       <c r="L24" s="19">
         <v>49</v>
@@ -1525,10 +1789,10 @@
     </row>
     <row r="25" spans="1:19" x14ac:dyDescent="0.3">
       <c r="A25" s="1" t="s">
-        <v>58</v>
+        <v>56</v>
       </c>
       <c r="B25" s="22" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="C25" s="22">
         <v>594</v>
@@ -1550,7 +1814,7 @@
       </c>
       <c r="J25" s="13"/>
       <c r="K25" s="19" t="s">
-        <v>65</v>
+        <v>63</v>
       </c>
       <c r="L25" s="19">
         <v>52</v>
@@ -1565,10 +1829,10 @@
     </row>
     <row r="26" spans="1:19" x14ac:dyDescent="0.3">
       <c r="A26" s="1" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="B26" s="22" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="C26" s="22">
         <v>425</v>
@@ -1590,7 +1854,7 @@
       </c>
       <c r="J26" s="13"/>
       <c r="K26" s="19" t="s">
-        <v>66</v>
+        <v>64</v>
       </c>
       <c r="L26" s="19">
         <v>54</v>
@@ -1605,10 +1869,10 @@
     </row>
     <row r="27" spans="1:19" x14ac:dyDescent="0.3">
       <c r="A27" s="1" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="B27" s="22" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="C27" s="22">
         <v>1008</v>
@@ -1630,7 +1894,7 @@
       </c>
       <c r="J27" s="16"/>
       <c r="K27" s="19" t="s">
-        <v>67</v>
+        <v>65</v>
       </c>
       <c r="L27" s="19">
         <v>56</v>
@@ -1645,10 +1909,10 @@
     </row>
     <row r="28" spans="1:19" x14ac:dyDescent="0.3">
       <c r="A28" s="1" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="B28" s="22" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="C28" s="22">
         <v>512</v>
@@ -1670,7 +1934,7 @@
       </c>
       <c r="J28" s="16"/>
       <c r="K28" s="19" t="s">
-        <v>68</v>
+        <v>66</v>
       </c>
       <c r="L28" s="19">
         <v>58</v>
@@ -1685,10 +1949,10 @@
     </row>
     <row r="29" spans="1:19" x14ac:dyDescent="0.3">
       <c r="A29" s="1" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="B29" s="22" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="C29" s="22">
         <v>749</v>
@@ -1710,7 +1974,7 @@
       </c>
       <c r="J29" s="16"/>
       <c r="K29" s="19" t="s">
-        <v>69</v>
+        <v>67</v>
       </c>
       <c r="L29" s="19">
         <v>61</v>
@@ -1725,10 +1989,10 @@
     </row>
     <row r="30" spans="1:19" x14ac:dyDescent="0.3">
       <c r="A30" s="1" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="B30" s="22" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="C30" s="22">
         <v>466</v>
@@ -1761,10 +2025,10 @@
     </row>
     <row r="31" spans="1:19" x14ac:dyDescent="0.3">
       <c r="A31" s="1" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="B31" s="22" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="C31" s="22">
         <v>75.5</v>
@@ -1797,28 +2061,17 @@
     </row>
     <row r="32" spans="1:19" x14ac:dyDescent="0.3">
       <c r="A32" s="1" t="s">
-        <v>29</v>
-      </c>
-      <c r="B32" s="20"/>
-      <c r="C32" s="1">
-        <v>700</v>
-      </c>
-      <c r="D32" s="1">
-        <v>700</v>
-      </c>
-      <c r="E32" s="1">
-        <v>700</v>
-      </c>
-      <c r="F32" s="1">
-        <v>700</v>
-      </c>
-      <c r="G32" s="1">
-        <v>700</v>
-      </c>
-      <c r="H32" s="1">
-        <v>700</v>
-      </c>
-      <c r="I32"/>
+        <v>7</v>
+      </c>
+      <c r="B32" s="22"/>
+      <c r="C32" s="22"/>
+      <c r="D32" s="22"/>
+      <c r="E32" s="22"/>
+      <c r="F32" s="22">
+        <v>825</v>
+      </c>
+      <c r="G32" s="22"/>
+      <c r="H32" s="22"/>
       <c r="J32" s="16"/>
       <c r="K32" s="16"/>
       <c r="L32" s="16"/>
@@ -1832,28 +2085,29 @@
     </row>
     <row r="33" spans="1:19" x14ac:dyDescent="0.3">
       <c r="A33" s="1" t="s">
-        <v>30</v>
+        <v>28</v>
       </c>
       <c r="B33" s="20"/>
       <c r="C33" s="1">
-        <v>38</v>
+        <v>700</v>
       </c>
       <c r="D33" s="1">
-        <v>38</v>
+        <v>700</v>
       </c>
       <c r="E33" s="1">
-        <v>38</v>
+        <v>700</v>
       </c>
       <c r="F33" s="1">
-        <v>38</v>
+        <v>700</v>
       </c>
       <c r="G33" s="1">
-        <v>38</v>
+        <v>700</v>
       </c>
       <c r="H33" s="1">
-        <v>38</v>
-      </c>
-      <c r="J33" s="17"/>
+        <v>700</v>
+      </c>
+      <c r="I33"/>
+      <c r="J33" s="16"/>
       <c r="K33" s="16"/>
       <c r="L33" s="16"/>
       <c r="M33" s="16"/>
@@ -1866,28 +2120,28 @@
     </row>
     <row r="34" spans="1:19" x14ac:dyDescent="0.3">
       <c r="A34" s="1" t="s">
-        <v>31</v>
+        <v>29</v>
       </c>
       <c r="B34" s="20"/>
-      <c r="C34" s="20">
-        <v>47</v>
-      </c>
-      <c r="D34" s="20">
-        <v>47</v>
-      </c>
-      <c r="E34" s="20">
-        <v>47</v>
-      </c>
-      <c r="F34" s="20">
-        <v>47</v>
-      </c>
-      <c r="G34" s="20">
-        <v>47</v>
-      </c>
-      <c r="H34" s="20">
-        <v>47</v>
-      </c>
-      <c r="J34" s="16"/>
+      <c r="C34" s="1">
+        <v>38</v>
+      </c>
+      <c r="D34" s="1">
+        <v>38</v>
+      </c>
+      <c r="E34" s="1">
+        <v>38</v>
+      </c>
+      <c r="F34" s="1">
+        <v>38</v>
+      </c>
+      <c r="G34" s="1">
+        <v>38</v>
+      </c>
+      <c r="H34" s="1">
+        <v>38</v>
+      </c>
+      <c r="J34" s="17"/>
       <c r="K34" s="16"/>
       <c r="L34" s="16"/>
       <c r="M34" s="16"/>
@@ -1900,26 +2154,26 @@
     </row>
     <row r="35" spans="1:19" x14ac:dyDescent="0.3">
       <c r="A35" s="1" t="s">
-        <v>32</v>
-      </c>
+        <v>30</v>
+      </c>
+      <c r="B35" s="20"/>
       <c r="C35" s="20">
-        <v>155</v>
+        <v>47</v>
       </c>
       <c r="D35" s="20">
-        <f>AVERAGE(D37,C38)</f>
-        <v>160.5</v>
+        <v>47</v>
       </c>
       <c r="E35" s="20">
-        <v>168</v>
+        <v>47</v>
       </c>
       <c r="F35" s="20">
-        <v>175</v>
+        <v>47</v>
       </c>
       <c r="G35" s="20">
-        <v>183</v>
+        <v>47</v>
       </c>
       <c r="H35" s="20">
-        <v>191</v>
+        <v>47</v>
       </c>
       <c r="J35" s="16"/>
       <c r="K35" s="16"/>
@@ -1934,31 +2188,31 @@
     </row>
     <row r="36" spans="1:19" x14ac:dyDescent="0.3">
       <c r="A36" s="1" t="s">
-        <v>33</v>
-      </c>
-      <c r="C36" s="1">
-        <f>D35</f>
+        <v>31</v>
+      </c>
+      <c r="C36" s="20">
+        <v>155</v>
+      </c>
+      <c r="D36" s="20">
+        <f>AVERAGE(D38,C39)</f>
         <v>160.5</v>
       </c>
-      <c r="D36" s="1">
+      <c r="E36" s="20">
         <v>168</v>
       </c>
-      <c r="E36" s="1">
+      <c r="F36" s="20">
         <v>175</v>
       </c>
-      <c r="F36" s="1">
+      <c r="G36" s="20">
         <v>183</v>
       </c>
-      <c r="G36" s="1">
+      <c r="H36" s="20">
         <v>191</v>
       </c>
-      <c r="H36" s="1">
-        <v>200</v>
-      </c>
-      <c r="J36" s="14"/>
-      <c r="K36" s="14"/>
-      <c r="L36" s="14"/>
-      <c r="M36" s="14"/>
+      <c r="J36" s="16"/>
+      <c r="K36" s="16"/>
+      <c r="L36" s="16"/>
+      <c r="M36" s="16"/>
       <c r="N36" s="14"/>
       <c r="O36" s="14"/>
       <c r="P36" s="14"/>
@@ -1967,23 +2221,27 @@
       <c r="S36" s="14"/>
     </row>
     <row r="37" spans="1:19" x14ac:dyDescent="0.3">
-      <c r="C37" s="20">
-        <v>155</v>
-      </c>
-      <c r="D37" s="20">
-        <v>163</v>
-      </c>
-      <c r="E37" s="20">
+      <c r="A37" s="1" t="s">
+        <v>32</v>
+      </c>
+      <c r="C37" s="1">
+        <f>D36</f>
+        <v>160.5</v>
+      </c>
+      <c r="D37" s="1">
         <v>168</v>
       </c>
-      <c r="F37" s="20">
+      <c r="E37" s="1">
         <v>175</v>
       </c>
-      <c r="G37" s="20">
+      <c r="F37" s="1">
         <v>183</v>
       </c>
-      <c r="H37" s="20">
+      <c r="G37" s="1">
         <v>191</v>
+      </c>
+      <c r="H37" s="1">
+        <v>200</v>
       </c>
       <c r="J37" s="14"/>
       <c r="K37" s="14"/>
@@ -1997,40 +2255,61 @@
       <c r="S37" s="14"/>
     </row>
     <row r="38" spans="1:19" x14ac:dyDescent="0.3">
-      <c r="C38" s="1">
+      <c r="C38" s="20">
+        <v>155</v>
+      </c>
+      <c r="D38" s="20">
+        <v>163</v>
+      </c>
+      <c r="E38" s="20">
+        <v>168</v>
+      </c>
+      <c r="F38" s="20">
+        <v>175</v>
+      </c>
+      <c r="G38" s="20">
+        <v>183</v>
+      </c>
+      <c r="H38" s="20">
+        <v>191</v>
+      </c>
+      <c r="J38" s="14"/>
+      <c r="K38" s="14"/>
+      <c r="L38" s="14"/>
+      <c r="M38" s="14"/>
+      <c r="N38" s="14"/>
+      <c r="O38" s="14"/>
+      <c r="P38" s="14"/>
+      <c r="Q38" s="14"/>
+      <c r="R38" s="14"/>
+      <c r="S38" s="14"/>
+    </row>
+    <row r="39" spans="1:19" x14ac:dyDescent="0.3">
+      <c r="C39" s="1">
         <v>158</v>
       </c>
-      <c r="D38" s="1">
+      <c r="D39" s="1">
         <v>168</v>
       </c>
-      <c r="E38" s="1">
+      <c r="E39" s="1">
         <v>175</v>
       </c>
-      <c r="F38" s="1">
+      <c r="F39" s="1">
         <v>183</v>
       </c>
-      <c r="G38" s="1">
+      <c r="G39" s="1">
         <v>191</v>
       </c>
-      <c r="H38" s="1">
+      <c r="H39" s="1">
         <v>200</v>
       </c>
     </row>
-    <row r="39" spans="1:19" ht="27" x14ac:dyDescent="0.3">
-      <c r="B39" s="8"/>
-    </row>
-    <row r="40" spans="1:19" ht="30" x14ac:dyDescent="0.45">
+    <row r="40" spans="1:19" ht="27" x14ac:dyDescent="0.3">
       <c r="B40" s="8"/>
-      <c r="K40" s="9"/>
-      <c r="L40"/>
-      <c r="M40"/>
-      <c r="N40"/>
-      <c r="O40"/>
-      <c r="P40"/>
-    </row>
-    <row r="41" spans="1:19" ht="27" x14ac:dyDescent="0.3">
+    </row>
+    <row r="41" spans="1:19" ht="30" x14ac:dyDescent="0.45">
       <c r="B41" s="8"/>
-      <c r="K41" s="10"/>
+      <c r="K41" s="9"/>
       <c r="L41"/>
       <c r="M41"/>
       <c r="N41"/>
@@ -2039,17 +2318,12 @@
     </row>
     <row r="42" spans="1:19" ht="27" x14ac:dyDescent="0.3">
       <c r="B42" s="8"/>
-      <c r="C42" s="4"/>
-      <c r="D42" s="4"/>
-      <c r="E42" s="4"/>
-      <c r="F42" s="4"/>
-      <c r="G42" s="4"/>
-      <c r="K42" s="11"/>
-      <c r="L42" s="11"/>
-      <c r="M42" s="11"/>
-      <c r="N42" s="11"/>
-      <c r="O42" s="11"/>
-      <c r="P42" s="11"/>
+      <c r="K42" s="10"/>
+      <c r="L42"/>
+      <c r="M42"/>
+      <c r="N42"/>
+      <c r="O42"/>
+      <c r="P42"/>
     </row>
     <row r="43" spans="1:19" ht="27" x14ac:dyDescent="0.3">
       <c r="B43" s="8"/>
@@ -2059,14 +2333,19 @@
       <c r="F43" s="4"/>
       <c r="G43" s="4"/>
       <c r="K43" s="11"/>
-      <c r="L43" s="12"/>
-      <c r="M43" s="12"/>
-      <c r="N43" s="12"/>
-      <c r="O43" s="12"/>
-      <c r="P43" s="12"/>
+      <c r="L43" s="11"/>
+      <c r="M43" s="11"/>
+      <c r="N43" s="11"/>
+      <c r="O43" s="11"/>
+      <c r="P43" s="11"/>
     </row>
     <row r="44" spans="1:19" ht="27" x14ac:dyDescent="0.3">
       <c r="B44" s="8"/>
+      <c r="C44" s="4"/>
+      <c r="D44" s="4"/>
+      <c r="E44" s="4"/>
+      <c r="F44" s="4"/>
+      <c r="G44" s="4"/>
       <c r="K44" s="11"/>
       <c r="L44" s="12"/>
       <c r="M44" s="12"/>
@@ -2074,7 +2353,8 @@
       <c r="O44" s="12"/>
       <c r="P44" s="12"/>
     </row>
-    <row r="45" spans="1:19" x14ac:dyDescent="0.3">
+    <row r="45" spans="1:19" ht="27" x14ac:dyDescent="0.3">
+      <c r="B45" s="8"/>
       <c r="K45" s="11"/>
       <c r="L45" s="12"/>
       <c r="M45" s="12"/>
@@ -2082,6 +2362,24 @@
       <c r="O45" s="12"/>
       <c r="P45" s="12"/>
     </row>
+    <row r="46" spans="1:19" x14ac:dyDescent="0.3">
+      <c r="K46" s="11"/>
+      <c r="L46" s="12"/>
+      <c r="M46" s="12"/>
+      <c r="N46" s="12"/>
+      <c r="O46" s="12"/>
+      <c r="P46" s="12"/>
+    </row>
+    <row r="67" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A67" s="1" t="s">
+        <v>95</v>
+      </c>
+    </row>
+    <row r="68" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A68" s="1" t="s">
+        <v>96</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <drawing r:id="rId1"/>

--- a/data/gravel/Specialized Crux 2025.xlsx
+++ b/data/gravel/Specialized Crux 2025.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10713"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10928"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/walker/Documents/Github/Bike Geometry Project/data/gravel copy/"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/walker/Documents/Github/Bike Geometry Project/data/gravel/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B660000C-8BF8-F24B-B60C-195D1E98E324}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{5A3B0508-BD7F-2D4A-B79A-C8157182137D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="500" windowWidth="13120" windowHeight="6100" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="0" yWindow="500" windowWidth="19940" windowHeight="16200" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="131" uniqueCount="127">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="127" uniqueCount="127">
   <si>
     <t>brand</t>
   </si>
@@ -1557,32 +1557,20 @@
       <c r="A46" t="s">
         <v>80</v>
       </c>
-      <c r="B46" t="s">
-        <v>81</v>
-      </c>
     </row>
     <row r="47" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A47" t="s">
         <v>82</v>
       </c>
-      <c r="B47" t="s">
-        <v>81</v>
-      </c>
     </row>
     <row r="48" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A48" t="s">
         <v>83</v>
       </c>
-      <c r="B48" t="s">
-        <v>81</v>
-      </c>
     </row>
     <row r="49" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A49" t="s">
         <v>84</v>
-      </c>
-      <c r="B49" t="s">
-        <v>81</v>
       </c>
     </row>
     <row r="50" spans="1:2" x14ac:dyDescent="0.3">

--- a/data/gravel/Specialized Crux 2025.xlsx
+++ b/data/gravel/Specialized Crux 2025.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10928"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="11003"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/walker/Documents/Github/Bike Geometry Project/data/gravel/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{5A3B0508-BD7F-2D4A-B79A-C8157182137D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{FB9C807E-1D0B-8D46-9F01-75A2EFDCF157}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="0" yWindow="500" windowWidth="19940" windowHeight="16200" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="127" uniqueCount="127">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="128" uniqueCount="128">
   <si>
     <t>brand</t>
   </si>
@@ -46,9 +46,6 @@
     <t>URL</t>
   </si>
   <si>
-    <t>https://www.specialized.com/us/en/s-works-crux-sram-red-xplr/p/4223480?color=5381911-4223480</t>
-  </si>
-  <si>
     <t>17-Jul-2025</t>
   </si>
   <si>
@@ -401,6 +398,12 @@
   </si>
   <si>
     <t>rigid</t>
+  </si>
+  <si>
+    <t>https://www.specialized.com/us/en/shop/bikes/gravel-bikes/crux</t>
+  </si>
+  <si>
+    <t>https://assets.specialized.com/i/specialized/91426-10_CRUX-PRO-NBLMET-SHDWSIL-SMK_HERO-PDP?$scom-pdp-gallery-image$&amp;fmt=webp</t>
   </si>
 </sst>
 </file>
@@ -767,7 +770,7 @@
         <v>6</v>
       </c>
       <c r="B4" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
     </row>
     <row r="5" spans="1:8" x14ac:dyDescent="0.3">
@@ -775,49 +778,54 @@
         <v>7</v>
       </c>
       <c r="B5" t="s">
-        <v>8</v>
+        <v>126</v>
+      </c>
+    </row>
+    <row r="6" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="B6" t="s">
+        <v>127</v>
       </c>
     </row>
     <row r="7" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A7" t="s">
+        <v>9</v>
+      </c>
+      <c r="B7" t="s">
         <v>10</v>
-      </c>
-      <c r="B7" t="s">
-        <v>11</v>
       </c>
     </row>
     <row r="8" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A8" t="s">
+        <v>11</v>
+      </c>
+      <c r="B8" t="s">
         <v>12</v>
       </c>
-      <c r="B8" t="s">
+      <c r="C8" t="s">
         <v>13</v>
       </c>
-      <c r="C8" t="s">
+      <c r="D8" t="s">
         <v>14</v>
       </c>
-      <c r="D8" t="s">
+      <c r="E8" t="s">
         <v>15</v>
       </c>
-      <c r="E8" t="s">
+      <c r="F8" t="s">
         <v>16</v>
       </c>
-      <c r="F8" t="s">
+      <c r="G8" t="s">
         <v>17</v>
       </c>
-      <c r="G8" t="s">
+      <c r="H8" t="s">
         <v>18</v>
-      </c>
-      <c r="H8" t="s">
-        <v>19</v>
       </c>
     </row>
     <row r="9" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A9" t="s">
+        <v>19</v>
+      </c>
+      <c r="B9" t="s">
         <v>20</v>
-      </c>
-      <c r="B9" t="s">
-        <v>21</v>
       </c>
       <c r="C9">
         <v>165</v>
@@ -840,10 +848,10 @@
     </row>
     <row r="10" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A10" t="s">
+        <v>21</v>
+      </c>
+      <c r="B10" t="s">
         <v>22</v>
-      </c>
-      <c r="B10" t="s">
-        <v>23</v>
       </c>
       <c r="C10">
         <v>380</v>
@@ -866,10 +874,10 @@
     </row>
     <row r="11" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A11" t="s">
+        <v>23</v>
+      </c>
+      <c r="B11" t="s">
         <v>24</v>
-      </c>
-      <c r="B11" t="s">
-        <v>25</v>
       </c>
       <c r="C11">
         <v>70</v>
@@ -892,10 +900,10 @@
     </row>
     <row r="12" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A12" t="s">
+        <v>25</v>
+      </c>
+      <c r="B12" t="s">
         <v>26</v>
-      </c>
-      <c r="B12" t="s">
-        <v>27</v>
       </c>
       <c r="C12">
         <v>155</v>
@@ -918,10 +926,10 @@
     </row>
     <row r="13" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A13" t="s">
+        <v>27</v>
+      </c>
+      <c r="B13" t="s">
         <v>28</v>
-      </c>
-      <c r="B13" t="s">
-        <v>29</v>
       </c>
       <c r="C13">
         <v>300</v>
@@ -944,10 +952,10 @@
     </row>
     <row r="14" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A14" t="s">
+        <v>29</v>
+      </c>
+      <c r="B14" t="s">
         <v>30</v>
-      </c>
-      <c r="B14" t="s">
-        <v>31</v>
       </c>
       <c r="C14">
         <v>530</v>
@@ -970,10 +978,10 @@
     </row>
     <row r="15" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A15" t="s">
+        <v>31</v>
+      </c>
+      <c r="B15" t="s">
         <v>32</v>
-      </c>
-      <c r="B15" t="s">
-        <v>33</v>
       </c>
       <c r="C15">
         <v>375</v>
@@ -996,10 +1004,10 @@
     </row>
     <row r="16" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A16" t="s">
+        <v>33</v>
+      </c>
+      <c r="B16" t="s">
         <v>34</v>
-      </c>
-      <c r="B16" t="s">
-        <v>35</v>
       </c>
       <c r="C16">
         <v>100</v>
@@ -1022,10 +1030,10 @@
     </row>
     <row r="17" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A17" t="s">
+        <v>35</v>
+      </c>
+      <c r="B17" t="s">
         <v>36</v>
-      </c>
-      <c r="B17" t="s">
-        <v>37</v>
       </c>
       <c r="C17">
         <v>70.5</v>
@@ -1048,10 +1056,10 @@
     </row>
     <row r="18" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A18" t="s">
+        <v>37</v>
+      </c>
+      <c r="B18" t="s">
         <v>38</v>
-      </c>
-      <c r="B18" t="s">
-        <v>39</v>
       </c>
       <c r="C18">
         <v>284</v>
@@ -1074,10 +1082,10 @@
     </row>
     <row r="19" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A19" t="s">
+        <v>39</v>
+      </c>
+      <c r="B19" t="s">
         <v>40</v>
-      </c>
-      <c r="B19" t="s">
-        <v>41</v>
       </c>
       <c r="C19">
         <v>74</v>
@@ -1100,10 +1108,10 @@
     </row>
     <row r="20" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A20" t="s">
+        <v>41</v>
+      </c>
+      <c r="B20" t="s">
         <v>42</v>
-      </c>
-      <c r="B20" t="s">
-        <v>43</v>
       </c>
       <c r="C20">
         <v>74</v>
@@ -1126,10 +1134,10 @@
     </row>
     <row r="21" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A21" t="s">
+        <v>43</v>
+      </c>
+      <c r="B21" t="s">
         <v>44</v>
-      </c>
-      <c r="B21" t="s">
-        <v>45</v>
       </c>
       <c r="C21">
         <v>401</v>
@@ -1152,10 +1160,10 @@
     </row>
     <row r="22" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A22" t="s">
+        <v>45</v>
+      </c>
+      <c r="B22" t="s">
         <v>46</v>
-      </c>
-      <c r="B22" t="s">
-        <v>47</v>
       </c>
       <c r="C22">
         <v>50</v>
@@ -1178,10 +1186,10 @@
     </row>
     <row r="23" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A23" t="s">
+        <v>47</v>
+      </c>
+      <c r="B23" t="s">
         <v>48</v>
-      </c>
-      <c r="B23" t="s">
-        <v>49</v>
       </c>
       <c r="C23">
         <v>594</v>
@@ -1204,10 +1212,10 @@
     </row>
     <row r="24" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A24" t="s">
+        <v>49</v>
+      </c>
+      <c r="B24" t="s">
         <v>50</v>
-      </c>
-      <c r="B24" t="s">
-        <v>51</v>
       </c>
       <c r="C24">
         <v>425</v>
@@ -1230,10 +1238,10 @@
     </row>
     <row r="25" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A25" t="s">
+        <v>51</v>
+      </c>
+      <c r="B25" t="s">
         <v>52</v>
-      </c>
-      <c r="B25" t="s">
-        <v>53</v>
       </c>
       <c r="C25">
         <v>1008</v>
@@ -1256,10 +1264,10 @@
     </row>
     <row r="26" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A26" t="s">
+        <v>53</v>
+      </c>
+      <c r="B26" t="s">
         <v>54</v>
-      </c>
-      <c r="B26" t="s">
-        <v>55</v>
       </c>
       <c r="C26">
         <v>512</v>
@@ -1282,10 +1290,10 @@
     </row>
     <row r="27" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A27" t="s">
+        <v>55</v>
+      </c>
+      <c r="B27" t="s">
         <v>56</v>
-      </c>
-      <c r="B27" t="s">
-        <v>57</v>
       </c>
       <c r="C27">
         <v>749</v>
@@ -1308,10 +1316,10 @@
     </row>
     <row r="28" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A28" t="s">
+        <v>57</v>
+      </c>
+      <c r="B28" t="s">
         <v>58</v>
-      </c>
-      <c r="B28" t="s">
-        <v>59</v>
       </c>
       <c r="C28">
         <v>466</v>
@@ -1334,10 +1342,10 @@
     </row>
     <row r="29" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A29" t="s">
+        <v>59</v>
+      </c>
+      <c r="B29" t="s">
         <v>60</v>
-      </c>
-      <c r="B29" t="s">
-        <v>61</v>
       </c>
       <c r="C29">
         <v>75.5</v>
@@ -1360,7 +1368,7 @@
     </row>
     <row r="30" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A30" t="s">
-        <v>62</v>
+        <v>61</v>
       </c>
       <c r="F30">
         <v>825</v>
@@ -1368,7 +1376,7 @@
     </row>
     <row r="31" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A31" t="s">
-        <v>63</v>
+        <v>62</v>
       </c>
       <c r="C31">
         <v>700</v>
@@ -1391,7 +1399,7 @@
     </row>
     <row r="32" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A32" t="s">
-        <v>64</v>
+        <v>63</v>
       </c>
       <c r="C32">
         <v>38</v>
@@ -1414,7 +1422,7 @@
     </row>
     <row r="33" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A33" t="s">
-        <v>65</v>
+        <v>64</v>
       </c>
       <c r="C33">
         <v>47</v>
@@ -1437,7 +1445,7 @@
     </row>
     <row r="34" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A34" t="s">
-        <v>66</v>
+        <v>65</v>
       </c>
       <c r="C34">
         <v>155</v>
@@ -1460,7 +1468,7 @@
     </row>
     <row r="35" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A35" t="s">
-        <v>67</v>
+        <v>66</v>
       </c>
       <c r="C35">
         <v>160.5</v>
@@ -1483,257 +1491,257 @@
     </row>
     <row r="37" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A37" t="s">
+        <v>67</v>
+      </c>
+      <c r="B37" t="s">
         <v>68</v>
-      </c>
-      <c r="B37" t="s">
-        <v>69</v>
       </c>
     </row>
     <row r="38" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A38" t="s">
+        <v>120</v>
+      </c>
+      <c r="B38" t="s">
         <v>121</v>
-      </c>
-      <c r="B38" t="s">
-        <v>122</v>
       </c>
     </row>
     <row r="39" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A39" t="s">
+        <v>122</v>
+      </c>
+      <c r="B39" t="s">
         <v>123</v>
-      </c>
-      <c r="B39" t="s">
-        <v>124</v>
       </c>
     </row>
     <row r="40" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A40" t="s">
+        <v>124</v>
+      </c>
+      <c r="B40" t="s">
         <v>125</v>
-      </c>
-      <c r="B40" t="s">
-        <v>126</v>
       </c>
     </row>
     <row r="41" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A41" t="s">
+        <v>69</v>
+      </c>
+      <c r="B41" t="s">
         <v>70</v>
-      </c>
-      <c r="B41" t="s">
-        <v>71</v>
       </c>
     </row>
     <row r="42" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A42" t="s">
+        <v>71</v>
+      </c>
+      <c r="B42" t="s">
         <v>72</v>
-      </c>
-      <c r="B42" t="s">
-        <v>73</v>
       </c>
     </row>
     <row r="43" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A43" t="s">
+        <v>73</v>
+      </c>
+      <c r="B43" t="s">
         <v>74</v>
-      </c>
-      <c r="B43" t="s">
-        <v>75</v>
       </c>
     </row>
     <row r="44" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A44" t="s">
+        <v>75</v>
+      </c>
+      <c r="B44" t="s">
         <v>76</v>
-      </c>
-      <c r="B44" t="s">
-        <v>77</v>
       </c>
     </row>
     <row r="45" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A45" t="s">
+        <v>77</v>
+      </c>
+      <c r="B45" t="s">
         <v>78</v>
-      </c>
-      <c r="B45" t="s">
-        <v>79</v>
       </c>
     </row>
     <row r="46" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A46" t="s">
-        <v>80</v>
+        <v>79</v>
       </c>
     </row>
     <row r="47" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A47" t="s">
-        <v>82</v>
+        <v>81</v>
       </c>
     </row>
     <row r="48" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A48" t="s">
-        <v>83</v>
+        <v>82</v>
       </c>
     </row>
     <row r="49" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A49" t="s">
-        <v>84</v>
+        <v>83</v>
       </c>
     </row>
     <row r="50" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A50" t="s">
+        <v>84</v>
+      </c>
+      <c r="B50" t="s">
         <v>85</v>
-      </c>
-      <c r="B50" t="s">
-        <v>86</v>
       </c>
     </row>
     <row r="51" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A51" t="s">
+        <v>86</v>
+      </c>
+      <c r="B51" t="s">
         <v>87</v>
-      </c>
-      <c r="B51" t="s">
-        <v>88</v>
       </c>
     </row>
     <row r="52" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A52" t="s">
+        <v>88</v>
+      </c>
+      <c r="B52" t="s">
         <v>89</v>
-      </c>
-      <c r="B52" t="s">
-        <v>90</v>
       </c>
     </row>
     <row r="53" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A53" t="s">
-        <v>91</v>
+        <v>90</v>
       </c>
     </row>
     <row r="54" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A54" t="s">
+        <v>91</v>
+      </c>
+      <c r="B54" t="s">
         <v>92</v>
-      </c>
-      <c r="B54" t="s">
-        <v>93</v>
       </c>
     </row>
     <row r="55" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A55" t="s">
+        <v>93</v>
+      </c>
+      <c r="B55" t="s">
         <v>94</v>
-      </c>
-      <c r="B55" t="s">
-        <v>95</v>
       </c>
     </row>
     <row r="56" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A56" t="s">
-        <v>96</v>
+        <v>95</v>
       </c>
     </row>
     <row r="57" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A57" t="s">
-        <v>97</v>
+        <v>96</v>
       </c>
     </row>
     <row r="58" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A58" t="s">
-        <v>98</v>
+        <v>97</v>
       </c>
     </row>
     <row r="59" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A59" t="s">
-        <v>99</v>
+        <v>98</v>
       </c>
     </row>
     <row r="60" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A60" t="s">
-        <v>100</v>
+        <v>99</v>
       </c>
     </row>
     <row r="61" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A61" t="s">
-        <v>101</v>
+        <v>100</v>
       </c>
     </row>
     <row r="62" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A62" t="s">
-        <v>102</v>
+        <v>101</v>
       </c>
     </row>
     <row r="63" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A63" t="s">
-        <v>103</v>
+        <v>102</v>
       </c>
     </row>
     <row r="64" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A64" t="s">
-        <v>104</v>
+        <v>103</v>
       </c>
       <c r="B64" t="s">
-        <v>81</v>
+        <v>80</v>
       </c>
     </row>
     <row r="65" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A65" t="s">
+        <v>104</v>
+      </c>
+      <c r="B65" t="s">
         <v>105</v>
-      </c>
-      <c r="B65" t="s">
-        <v>106</v>
       </c>
     </row>
     <row r="66" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A66" t="s">
+        <v>106</v>
+      </c>
+      <c r="B66" t="s">
         <v>107</v>
-      </c>
-      <c r="B66" t="s">
-        <v>108</v>
       </c>
     </row>
     <row r="67" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A67" t="s">
-        <v>109</v>
+        <v>108</v>
       </c>
     </row>
     <row r="68" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A68" t="s">
-        <v>110</v>
+        <v>109</v>
       </c>
     </row>
     <row r="69" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A69" t="s">
-        <v>111</v>
+        <v>110</v>
       </c>
     </row>
     <row r="70" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A70" t="s">
-        <v>112</v>
+        <v>111</v>
       </c>
     </row>
     <row r="71" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A71" t="s">
-        <v>113</v>
+        <v>112</v>
       </c>
     </row>
     <row r="72" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A72" t="s">
+        <v>113</v>
+      </c>
+      <c r="B72" t="s">
         <v>114</v>
-      </c>
-      <c r="B72" t="s">
-        <v>115</v>
       </c>
     </row>
     <row r="73" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A73" t="s">
+        <v>115</v>
+      </c>
+      <c r="B73" t="s">
         <v>116</v>
-      </c>
-      <c r="B73" t="s">
-        <v>117</v>
       </c>
     </row>
     <row r="74" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A74" t="s">
-        <v>118</v>
+        <v>117</v>
       </c>
     </row>
     <row r="75" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A75" t="s">
+        <v>118</v>
+      </c>
+      <c r="B75" t="s">
         <v>119</v>
-      </c>
-      <c r="B75" t="s">
-        <v>120</v>
       </c>
     </row>
   </sheetData>

--- a/data/gravel/Specialized Crux 2025.xlsx
+++ b/data/gravel/Specialized Crux 2025.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/walker/Documents/Github/Bike Geometry Project/data/gravel/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{FB9C807E-1D0B-8D46-9F01-75A2EFDCF157}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C141B6F5-4C83-564F-AD96-08E83758E96C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="0" yWindow="500" windowWidth="19940" windowHeight="16200" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -205,9 +205,6 @@
     <t>Seat Tube Angle</t>
   </si>
   <si>
-    <t>frame weight</t>
-  </si>
-  <si>
     <t>wheel_size</t>
   </si>
   <si>
@@ -404,17 +401,26 @@
   </si>
   <si>
     <t>https://assets.specialized.com/i/specialized/91426-10_CRUX-PRO-NBLMET-SHDWSIL-SMK_HERO-PDP?$scom-pdp-gallery-image$&amp;fmt=webp</t>
+  </si>
+  <si>
+    <t>frame_weight</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="1" x14ac:knownFonts="1">
+  <fonts count="2" x14ac:knownFonts="1">
     <font>
       <sz val="14"/>
       <color rgb="FF000000"/>
       <name val="Futura"/>
+    </font>
+    <font>
+      <sz val="14"/>
+      <color rgb="FF000000"/>
+      <name val="Futura"/>
+      <family val="2"/>
     </font>
   </fonts>
   <fills count="2">
@@ -437,8 +443,9 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="1">
+  <cellXfs count="2">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -778,12 +785,12 @@
         <v>7</v>
       </c>
       <c r="B5" t="s">
-        <v>126</v>
+        <v>125</v>
       </c>
     </row>
     <row r="6" spans="1:8" x14ac:dyDescent="0.3">
       <c r="B6" t="s">
-        <v>127</v>
+        <v>126</v>
       </c>
     </row>
     <row r="7" spans="1:8" x14ac:dyDescent="0.3">
@@ -1367,8 +1374,8 @@
       </c>
     </row>
     <row r="30" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A30" t="s">
-        <v>61</v>
+      <c r="A30" s="1" t="s">
+        <v>127</v>
       </c>
       <c r="F30">
         <v>825</v>
@@ -1376,7 +1383,7 @@
     </row>
     <row r="31" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A31" t="s">
-        <v>62</v>
+        <v>61</v>
       </c>
       <c r="C31">
         <v>700</v>
@@ -1399,7 +1406,7 @@
     </row>
     <row r="32" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A32" t="s">
-        <v>63</v>
+        <v>62</v>
       </c>
       <c r="C32">
         <v>38</v>
@@ -1422,7 +1429,7 @@
     </row>
     <row r="33" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A33" t="s">
-        <v>64</v>
+        <v>63</v>
       </c>
       <c r="C33">
         <v>47</v>
@@ -1445,7 +1452,7 @@
     </row>
     <row r="34" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A34" t="s">
-        <v>65</v>
+        <v>64</v>
       </c>
       <c r="C34">
         <v>155</v>
@@ -1468,7 +1475,7 @@
     </row>
     <row r="35" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A35" t="s">
-        <v>66</v>
+        <v>65</v>
       </c>
       <c r="C35">
         <v>160.5</v>
@@ -1491,257 +1498,257 @@
     </row>
     <row r="37" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A37" t="s">
+        <v>66</v>
+      </c>
+      <c r="B37" t="s">
         <v>67</v>
-      </c>
-      <c r="B37" t="s">
-        <v>68</v>
       </c>
     </row>
     <row r="38" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A38" t="s">
+        <v>119</v>
+      </c>
+      <c r="B38" t="s">
         <v>120</v>
-      </c>
-      <c r="B38" t="s">
-        <v>121</v>
       </c>
     </row>
     <row r="39" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A39" t="s">
+        <v>121</v>
+      </c>
+      <c r="B39" t="s">
         <v>122</v>
-      </c>
-      <c r="B39" t="s">
-        <v>123</v>
       </c>
     </row>
     <row r="40" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A40" t="s">
+        <v>123</v>
+      </c>
+      <c r="B40" t="s">
         <v>124</v>
-      </c>
-      <c r="B40" t="s">
-        <v>125</v>
       </c>
     </row>
     <row r="41" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A41" t="s">
+        <v>68</v>
+      </c>
+      <c r="B41" t="s">
         <v>69</v>
-      </c>
-      <c r="B41" t="s">
-        <v>70</v>
       </c>
     </row>
     <row r="42" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A42" t="s">
+        <v>70</v>
+      </c>
+      <c r="B42" t="s">
         <v>71</v>
-      </c>
-      <c r="B42" t="s">
-        <v>72</v>
       </c>
     </row>
     <row r="43" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A43" t="s">
+        <v>72</v>
+      </c>
+      <c r="B43" t="s">
         <v>73</v>
-      </c>
-      <c r="B43" t="s">
-        <v>74</v>
       </c>
     </row>
     <row r="44" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A44" t="s">
+        <v>74</v>
+      </c>
+      <c r="B44" t="s">
         <v>75</v>
-      </c>
-      <c r="B44" t="s">
-        <v>76</v>
       </c>
     </row>
     <row r="45" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A45" t="s">
+        <v>76</v>
+      </c>
+      <c r="B45" t="s">
         <v>77</v>
-      </c>
-      <c r="B45" t="s">
-        <v>78</v>
       </c>
     </row>
     <row r="46" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A46" t="s">
-        <v>79</v>
+        <v>78</v>
       </c>
     </row>
     <row r="47" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A47" t="s">
-        <v>81</v>
+        <v>80</v>
       </c>
     </row>
     <row r="48" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A48" t="s">
-        <v>82</v>
+        <v>81</v>
       </c>
     </row>
     <row r="49" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A49" t="s">
-        <v>83</v>
+        <v>82</v>
       </c>
     </row>
     <row r="50" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A50" t="s">
+        <v>83</v>
+      </c>
+      <c r="B50" t="s">
         <v>84</v>
-      </c>
-      <c r="B50" t="s">
-        <v>85</v>
       </c>
     </row>
     <row r="51" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A51" t="s">
+        <v>85</v>
+      </c>
+      <c r="B51" t="s">
         <v>86</v>
-      </c>
-      <c r="B51" t="s">
-        <v>87</v>
       </c>
     </row>
     <row r="52" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A52" t="s">
+        <v>87</v>
+      </c>
+      <c r="B52" t="s">
         <v>88</v>
-      </c>
-      <c r="B52" t="s">
-        <v>89</v>
       </c>
     </row>
     <row r="53" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A53" t="s">
-        <v>90</v>
+        <v>89</v>
       </c>
     </row>
     <row r="54" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A54" t="s">
+        <v>90</v>
+      </c>
+      <c r="B54" t="s">
         <v>91</v>
-      </c>
-      <c r="B54" t="s">
-        <v>92</v>
       </c>
     </row>
     <row r="55" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A55" t="s">
+        <v>92</v>
+      </c>
+      <c r="B55" t="s">
         <v>93</v>
-      </c>
-      <c r="B55" t="s">
-        <v>94</v>
       </c>
     </row>
     <row r="56" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A56" t="s">
-        <v>95</v>
+        <v>94</v>
       </c>
     </row>
     <row r="57" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A57" t="s">
-        <v>96</v>
+        <v>95</v>
       </c>
     </row>
     <row r="58" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A58" t="s">
-        <v>97</v>
+        <v>96</v>
       </c>
     </row>
     <row r="59" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A59" t="s">
-        <v>98</v>
+        <v>97</v>
       </c>
     </row>
     <row r="60" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A60" t="s">
-        <v>99</v>
+        <v>98</v>
       </c>
     </row>
     <row r="61" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A61" t="s">
-        <v>100</v>
+        <v>99</v>
       </c>
     </row>
     <row r="62" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A62" t="s">
-        <v>101</v>
+        <v>100</v>
       </c>
     </row>
     <row r="63" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A63" t="s">
-        <v>102</v>
+        <v>101</v>
       </c>
     </row>
     <row r="64" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A64" t="s">
-        <v>103</v>
+        <v>102</v>
       </c>
       <c r="B64" t="s">
-        <v>80</v>
+        <v>79</v>
       </c>
     </row>
     <row r="65" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A65" t="s">
+        <v>103</v>
+      </c>
+      <c r="B65" t="s">
         <v>104</v>
-      </c>
-      <c r="B65" t="s">
-        <v>105</v>
       </c>
     </row>
     <row r="66" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A66" t="s">
+        <v>105</v>
+      </c>
+      <c r="B66" t="s">
         <v>106</v>
-      </c>
-      <c r="B66" t="s">
-        <v>107</v>
       </c>
     </row>
     <row r="67" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A67" t="s">
-        <v>108</v>
+        <v>107</v>
       </c>
     </row>
     <row r="68" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A68" t="s">
-        <v>109</v>
+        <v>108</v>
       </c>
     </row>
     <row r="69" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A69" t="s">
-        <v>110</v>
+        <v>109</v>
       </c>
     </row>
     <row r="70" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A70" t="s">
-        <v>111</v>
+        <v>110</v>
       </c>
     </row>
     <row r="71" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A71" t="s">
-        <v>112</v>
+        <v>111</v>
       </c>
     </row>
     <row r="72" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A72" t="s">
+        <v>112</v>
+      </c>
+      <c r="B72" t="s">
         <v>113</v>
-      </c>
-      <c r="B72" t="s">
-        <v>114</v>
       </c>
     </row>
     <row r="73" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A73" t="s">
+        <v>114</v>
+      </c>
+      <c r="B73" t="s">
         <v>115</v>
-      </c>
-      <c r="B73" t="s">
-        <v>116</v>
       </c>
     </row>
     <row r="74" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A74" t="s">
-        <v>117</v>
+        <v>116</v>
       </c>
     </row>
     <row r="75" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A75" t="s">
+        <v>117</v>
+      </c>
+      <c r="B75" t="s">
         <v>118</v>
-      </c>
-      <c r="B75" t="s">
-        <v>119</v>
       </c>
     </row>
   </sheetData>

--- a/data/gravel/Specialized Crux 2025.xlsx
+++ b/data/gravel/Specialized Crux 2025.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/walker/Documents/Github/Bike Geometry Project/data/gravel/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C141B6F5-4C83-564F-AD96-08E83758E96C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C7A2ADD7-B05D-4046-903B-8DD88A416897}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="0" yWindow="500" windowWidth="19940" windowHeight="16200" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="128" uniqueCount="128">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="130" uniqueCount="130">
   <si>
     <t>brand</t>
   </si>
@@ -376,9 +376,6 @@
     <t>currency</t>
   </si>
   <si>
-    <t>us</t>
-  </si>
-  <si>
     <t>class</t>
   </si>
   <si>
@@ -404,6 +401,15 @@
   </si>
   <si>
     <t>frame_weight</t>
+  </si>
+  <si>
+    <t>USD</t>
+  </si>
+  <si>
+    <t>location</t>
+  </si>
+  <si>
+    <t>Morgan Hill, California, USA</t>
   </si>
 </sst>
 </file>
@@ -742,7 +748,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:H75"/>
+  <dimension ref="A1:H76"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="20" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="2" width="19.6640625" customWidth="1"/>
@@ -785,12 +791,12 @@
         <v>7</v>
       </c>
       <c r="B5" t="s">
-        <v>125</v>
+        <v>124</v>
       </c>
     </row>
     <row r="6" spans="1:8" x14ac:dyDescent="0.3">
       <c r="B6" t="s">
-        <v>126</v>
+        <v>125</v>
       </c>
     </row>
     <row r="7" spans="1:8" x14ac:dyDescent="0.3">
@@ -1375,7 +1381,7 @@
     </row>
     <row r="30" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A30" s="1" t="s">
-        <v>127</v>
+        <v>126</v>
       </c>
       <c r="F30">
         <v>825</v>
@@ -1506,26 +1512,26 @@
     </row>
     <row r="38" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A38" t="s">
+        <v>118</v>
+      </c>
+      <c r="B38" t="s">
         <v>119</v>
-      </c>
-      <c r="B38" t="s">
-        <v>120</v>
       </c>
     </row>
     <row r="39" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A39" t="s">
+        <v>120</v>
+      </c>
+      <c r="B39" t="s">
         <v>121</v>
-      </c>
-      <c r="B39" t="s">
-        <v>122</v>
       </c>
     </row>
     <row r="40" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A40" t="s">
+        <v>122</v>
+      </c>
+      <c r="B40" t="s">
         <v>123</v>
-      </c>
-      <c r="B40" t="s">
-        <v>124</v>
       </c>
     </row>
     <row r="41" spans="1:8" x14ac:dyDescent="0.3">
@@ -1747,8 +1753,16 @@
       <c r="A75" t="s">
         <v>117</v>
       </c>
-      <c r="B75" t="s">
-        <v>118</v>
+      <c r="B75" s="1" t="s">
+        <v>127</v>
+      </c>
+    </row>
+    <row r="76" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A76" s="1" t="s">
+        <v>128</v>
+      </c>
+      <c r="B76" t="s">
+        <v>129</v>
       </c>
     </row>
   </sheetData>

--- a/data/gravel/Specialized Crux 2025.xlsx
+++ b/data/gravel/Specialized Crux 2025.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="11003"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="11026"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/walker/Documents/Github/Bike Geometry Project/data/gravel/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C7A2ADD7-B05D-4046-903B-8DD88A416897}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F34EEFB1-6B04-9A4D-A0F6-9679F1A393AF}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="0" yWindow="500" windowWidth="19940" windowHeight="16200" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="130" uniqueCount="130">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="136" uniqueCount="136">
   <si>
     <t>brand</t>
   </si>
@@ -410,6 +410,24 @@
   </si>
   <si>
     <t>Morgan Hill, California, USA</t>
+  </si>
+  <si>
+    <t>head_tube_d</t>
+  </si>
+  <si>
+    <t>headset_upper</t>
+  </si>
+  <si>
+    <t>headset_lower</t>
+  </si>
+  <si>
+    <t>fork_steerer</t>
+  </si>
+  <si>
+    <t>fork_steerer_d</t>
+  </si>
+  <si>
+    <t>fork_material</t>
   </si>
 </sst>
 </file>
@@ -748,7 +766,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:H76"/>
+  <dimension ref="A1:H82"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="20" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="2" width="19.6640625" customWidth="1"/>
@@ -1612,156 +1630,186 @@
     </row>
     <row r="52" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A52" t="s">
-        <v>87</v>
-      </c>
-      <c r="B52" t="s">
-        <v>88</v>
+        <v>130</v>
       </c>
     </row>
     <row r="53" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A53" t="s">
-        <v>89</v>
+        <v>131</v>
       </c>
     </row>
     <row r="54" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A54" t="s">
-        <v>90</v>
-      </c>
-      <c r="B54" t="s">
-        <v>91</v>
+        <v>132</v>
       </c>
     </row>
     <row r="55" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A55" t="s">
-        <v>92</v>
-      </c>
-      <c r="B55" t="s">
-        <v>93</v>
+        <v>133</v>
       </c>
     </row>
     <row r="56" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A56" t="s">
-        <v>94</v>
+        <v>134</v>
       </c>
     </row>
     <row r="57" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A57" t="s">
-        <v>95</v>
+        <v>135</v>
       </c>
     </row>
     <row r="58" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A58" t="s">
-        <v>96</v>
+        <v>87</v>
+      </c>
+      <c r="B58" t="s">
+        <v>88</v>
       </c>
     </row>
     <row r="59" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A59" t="s">
-        <v>97</v>
+        <v>89</v>
       </c>
     </row>
     <row r="60" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A60" t="s">
-        <v>98</v>
+        <v>90</v>
+      </c>
+      <c r="B60" t="s">
+        <v>91</v>
       </c>
     </row>
     <row r="61" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A61" t="s">
-        <v>99</v>
+        <v>92</v>
+      </c>
+      <c r="B61" t="s">
+        <v>93</v>
       </c>
     </row>
     <row r="62" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A62" t="s">
-        <v>100</v>
+        <v>94</v>
       </c>
     </row>
     <row r="63" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A63" t="s">
-        <v>101</v>
+        <v>95</v>
       </c>
     </row>
     <row r="64" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A64" t="s">
-        <v>102</v>
-      </c>
-      <c r="B64" t="s">
-        <v>79</v>
+        <v>96</v>
       </c>
     </row>
     <row r="65" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A65" t="s">
-        <v>103</v>
-      </c>
-      <c r="B65" t="s">
-        <v>104</v>
+        <v>97</v>
       </c>
     </row>
     <row r="66" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A66" t="s">
-        <v>105</v>
-      </c>
-      <c r="B66" t="s">
-        <v>106</v>
+        <v>98</v>
       </c>
     </row>
     <row r="67" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A67" t="s">
-        <v>107</v>
+        <v>99</v>
       </c>
     </row>
     <row r="68" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A68" t="s">
-        <v>108</v>
+        <v>100</v>
       </c>
     </row>
     <row r="69" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A69" t="s">
-        <v>109</v>
+        <v>101</v>
       </c>
     </row>
     <row r="70" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A70" t="s">
-        <v>110</v>
+        <v>102</v>
+      </c>
+      <c r="B70" t="s">
+        <v>79</v>
       </c>
     </row>
     <row r="71" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A71" t="s">
-        <v>111</v>
+        <v>103</v>
+      </c>
+      <c r="B71" t="s">
+        <v>104</v>
       </c>
     </row>
     <row r="72" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A72" t="s">
-        <v>112</v>
+        <v>105</v>
       </c>
       <c r="B72" t="s">
-        <v>113</v>
+        <v>106</v>
       </c>
     </row>
     <row r="73" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A73" t="s">
-        <v>114</v>
-      </c>
-      <c r="B73" t="s">
-        <v>115</v>
+        <v>107</v>
       </c>
     </row>
     <row r="74" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A74" t="s">
-        <v>116</v>
+        <v>108</v>
       </c>
     </row>
     <row r="75" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A75" t="s">
+        <v>109</v>
+      </c>
+    </row>
+    <row r="76" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A76" t="s">
+        <v>110</v>
+      </c>
+    </row>
+    <row r="77" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A77" t="s">
+        <v>111</v>
+      </c>
+    </row>
+    <row r="78" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A78" t="s">
+        <v>112</v>
+      </c>
+      <c r="B78" t="s">
+        <v>113</v>
+      </c>
+    </row>
+    <row r="79" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A79" t="s">
+        <v>114</v>
+      </c>
+      <c r="B79" t="s">
+        <v>115</v>
+      </c>
+    </row>
+    <row r="80" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A80" t="s">
+        <v>116</v>
+      </c>
+    </row>
+    <row r="81" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A81" t="s">
         <v>117</v>
       </c>
-      <c r="B75" s="1" t="s">
+      <c r="B81" s="1" t="s">
         <v>127</v>
       </c>
     </row>
-    <row r="76" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A76" s="1" t="s">
+    <row r="82" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A82" s="1" t="s">
         <v>128</v>
       </c>
-      <c r="B76" t="s">
+      <c r="B82" t="s">
         <v>129</v>
       </c>
     </row>

--- a/data/gravel/Specialized Crux 2025.xlsx
+++ b/data/gravel/Specialized Crux 2025.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="11026"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="11116"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/walker/Documents/Github/Bike Geometry Project/data/gravel/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F34EEFB1-6B04-9A4D-A0F6-9679F1A393AF}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B43DF7D6-AFBC-EF4F-B050-EAE03051C72E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="0" yWindow="500" windowWidth="19940" windowHeight="16200" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="136" uniqueCount="136">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="135" uniqueCount="134">
   <si>
     <t>brand</t>
   </si>
@@ -295,13 +295,7 @@
     <t>seatpost_diameter</t>
   </si>
   <si>
-    <t>31.6</t>
-  </si>
-  <si>
     <t>front_derailleur</t>
-  </si>
-  <si>
-    <t>adapter</t>
   </si>
   <si>
     <t>max_chainring_1x</t>
@@ -809,12 +803,12 @@
         <v>7</v>
       </c>
       <c r="B5" t="s">
-        <v>124</v>
+        <v>122</v>
       </c>
     </row>
     <row r="6" spans="1:8" x14ac:dyDescent="0.3">
       <c r="B6" t="s">
-        <v>125</v>
+        <v>123</v>
       </c>
     </row>
     <row r="7" spans="1:8" x14ac:dyDescent="0.3">
@@ -1399,7 +1393,7 @@
     </row>
     <row r="30" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A30" s="1" t="s">
-        <v>126</v>
+        <v>124</v>
       </c>
       <c r="F30">
         <v>825</v>
@@ -1530,26 +1524,26 @@
     </row>
     <row r="38" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A38" t="s">
-        <v>118</v>
+        <v>116</v>
       </c>
       <c r="B38" t="s">
-        <v>119</v>
+        <v>117</v>
       </c>
     </row>
     <row r="39" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A39" t="s">
-        <v>120</v>
+        <v>118</v>
       </c>
       <c r="B39" t="s">
-        <v>121</v>
+        <v>119</v>
       </c>
     </row>
     <row r="40" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A40" t="s">
-        <v>122</v>
+        <v>120</v>
       </c>
       <c r="B40" t="s">
-        <v>123</v>
+        <v>121</v>
       </c>
     </row>
     <row r="41" spans="1:8" x14ac:dyDescent="0.3">
@@ -1630,32 +1624,32 @@
     </row>
     <row r="52" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A52" t="s">
-        <v>130</v>
+        <v>128</v>
       </c>
     </row>
     <row r="53" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A53" t="s">
-        <v>131</v>
+        <v>129</v>
       </c>
     </row>
     <row r="54" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A54" t="s">
-        <v>132</v>
+        <v>130</v>
       </c>
     </row>
     <row r="55" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A55" t="s">
-        <v>133</v>
+        <v>131</v>
       </c>
     </row>
     <row r="56" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A56" t="s">
-        <v>134</v>
+        <v>132</v>
       </c>
     </row>
     <row r="57" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A57" t="s">
-        <v>135</v>
+        <v>133</v>
       </c>
     </row>
     <row r="58" spans="1:2" x14ac:dyDescent="0.3">
@@ -1675,61 +1669,61 @@
       <c r="A60" t="s">
         <v>90</v>
       </c>
-      <c r="B60" t="s">
-        <v>91</v>
+      <c r="B60">
+        <v>27.2</v>
       </c>
     </row>
     <row r="61" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A61" t="s">
-        <v>92</v>
-      </c>
-      <c r="B61" t="s">
-        <v>93</v>
+        <v>91</v>
+      </c>
+      <c r="B61" s="1" t="s">
+        <v>71</v>
       </c>
     </row>
     <row r="62" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A62" t="s">
-        <v>94</v>
+        <v>92</v>
       </c>
     </row>
     <row r="63" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A63" t="s">
-        <v>95</v>
+        <v>93</v>
       </c>
     </row>
     <row r="64" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A64" t="s">
-        <v>96</v>
+        <v>94</v>
       </c>
     </row>
     <row r="65" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A65" t="s">
-        <v>97</v>
+        <v>95</v>
       </c>
     </row>
     <row r="66" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A66" t="s">
-        <v>98</v>
+        <v>96</v>
       </c>
     </row>
     <row r="67" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A67" t="s">
-        <v>99</v>
+        <v>97</v>
       </c>
     </row>
     <row r="68" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A68" t="s">
-        <v>100</v>
+        <v>98</v>
       </c>
     </row>
     <row r="69" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A69" t="s">
-        <v>101</v>
+        <v>99</v>
       </c>
     </row>
     <row r="70" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A70" t="s">
-        <v>102</v>
+        <v>100</v>
       </c>
       <c r="B70" t="s">
         <v>79</v>
@@ -1737,80 +1731,80 @@
     </row>
     <row r="71" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A71" t="s">
-        <v>103</v>
+        <v>101</v>
       </c>
       <c r="B71" t="s">
-        <v>104</v>
+        <v>102</v>
       </c>
     </row>
     <row r="72" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A72" t="s">
-        <v>105</v>
+        <v>103</v>
       </c>
       <c r="B72" t="s">
-        <v>106</v>
+        <v>104</v>
       </c>
     </row>
     <row r="73" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A73" t="s">
-        <v>107</v>
+        <v>105</v>
       </c>
     </row>
     <row r="74" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A74" t="s">
-        <v>108</v>
+        <v>106</v>
       </c>
     </row>
     <row r="75" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A75" t="s">
-        <v>109</v>
+        <v>107</v>
       </c>
     </row>
     <row r="76" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A76" t="s">
-        <v>110</v>
+        <v>108</v>
       </c>
     </row>
     <row r="77" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A77" t="s">
-        <v>111</v>
+        <v>109</v>
       </c>
     </row>
     <row r="78" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A78" t="s">
-        <v>112</v>
+        <v>110</v>
       </c>
       <c r="B78" t="s">
-        <v>113</v>
+        <v>111</v>
       </c>
     </row>
     <row r="79" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A79" t="s">
-        <v>114</v>
+        <v>112</v>
       </c>
       <c r="B79" t="s">
-        <v>115</v>
+        <v>113</v>
       </c>
     </row>
     <row r="80" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A80" t="s">
-        <v>116</v>
+        <v>114</v>
       </c>
     </row>
     <row r="81" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A81" t="s">
-        <v>117</v>
+        <v>115</v>
       </c>
       <c r="B81" s="1" t="s">
-        <v>127</v>
+        <v>125</v>
       </c>
     </row>
     <row r="82" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A82" s="1" t="s">
-        <v>128</v>
+        <v>126</v>
       </c>
       <c r="B82" t="s">
-        <v>129</v>
+        <v>127</v>
       </c>
     </row>
   </sheetData>
